--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Suman magar</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9803822103</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9803822103</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -940,10 +938,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -954,7 +950,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -512,13 +512,13 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="35" customWidth="1" min="31" max="31"/>
+    <col width="40" customWidth="1" min="31" max="31"/>
     <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,10 +529,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -976,6 +976,209 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 9:46 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Client is asking for technical team</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349795</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9823765832</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:46:56 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849220717</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:05:36 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:46:56 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Pako Newroad Tamrakar Complex Near By Tamrakar Complex - Pako Newroad Tamrakar Complex Near By Tamra</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB161A</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -990,11 +1193,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -1027,7 +1230,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1109,7 +1312,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1124,134 +1327,175 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1036,20 +1036,14 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9823765832</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9823765832</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1121,10 +1115,8 @@
           <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="inlineStr"/>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1139,10 +1131,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1153,32 +1143,238 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>21h 41m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:01 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 9:57 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1230,7 +1426,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1345,73 +1541,64 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1426,76 +1613,114 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -510,26 +510,26 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="38" customWidth="1" min="33" max="33"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1378,6 +1378,639 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>sign in issue</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350187</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841418112</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841418112</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:59:56 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.743545</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Thapa Complex,P8RM+QM5, Bashundhara Ring Rd Track S, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>tmanisha4271@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>05:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.33514</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9840344764</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9880368739</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.69903</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Dahachok, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9880368739@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.24414</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840344764</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9880368739</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.69903</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Dahachok, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9880368739@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.24414</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1389,20 +2022,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1426,7 +2059,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1436,7 +2069,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1447,7 +2080,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -1459,7 +2092,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4d 9h 30m</t>
         </is>
       </c>
     </row>
@@ -1471,7 +2104,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4d 16h 45m</t>
         </is>
       </c>
     </row>
@@ -1512,14 +2145,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1616,113 +2249,360 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350187</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:59:56 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1445,10 +1445,8 @@
           <t>Manisha Thapa</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841418112</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841418112</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1483,10 +1481,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.743545</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.743545</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1542,25 +1538,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.33514</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.33514</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1656,10 +1648,8 @@
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9840344764</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9840344764</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1694,10 +1684,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.69903</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.69903</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1753,25 +1741,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.24414</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.24414</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -1867,10 +1851,8 @@
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840344764</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840344764</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1905,10 +1887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.69903</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.69903</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -1964,50 +1944,468 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.24414</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.24414</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>6d 14h 15m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>6d 15h 25m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>frequent slow internet</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350306</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Rai</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Rai</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9818698257</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37:35 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851147880</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:56:44 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37:35 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.73288</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Kapan police station ,Budhanilkantha 44600, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>dipakrai057@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>04:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L9-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.35932</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349298</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>RAJENDRA BAJRACHARYA</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>RAJENDRA BAJRACHARYA</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9869562347</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:25:28 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9851077389</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:25:28 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32:50 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.69838</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu KALIMATI kalimati ganesh man singh path, , ,</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>rojanbajr@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>10:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.299</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2420,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -2059,7 +2457,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2069,7 +2467,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2080,7 +2478,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2490,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4d 9h 30m</t>
+          <t>2d 20h 43m</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2502,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4d 16h 45m</t>
+          <t>3d 4h 49m</t>
         </is>
       </c>
     </row>
@@ -2141,127 +2539,122 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2277,332 +2670,512 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342919</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Mission shrestha</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-No internet connection on STB</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>6d 14h 15m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1350187</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:59:56 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>TKT1342919</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>6d 14h 15m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>6d 15h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350306</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Dipak Rai</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37:35 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:56:44 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37:35 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349298</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>RAJENDRA BAJRACHARYA</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:25:28 AM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:25:28 AM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32:50 AM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2054,10 +2054,8 @@
           <t>Dipak Rai</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9818698257</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9818698257</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2092,10 +2090,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.73288</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.73288</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2151,25 +2147,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L9-6</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.35932</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.35932</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2265,10 +2257,8 @@
           <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9869562347</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9869562347</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2303,10 +2293,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.69838</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.69838</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2362,48 +2350,354 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.299</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.29900000000001</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 7m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 7m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:51 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349403</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Chausara Rai</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Chausara Rai</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9849445856</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00:23 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9849445856</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:53:58 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00:32 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.73813</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near Seven Summit Treks Pvt. Ltd., Kapan, Budhanilkantha-11, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>11:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L18-4</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.35905</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2420,7 +2714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2457,7 +2751,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2467,7 +2761,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2478,7 +2772,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2784,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2d 20h 43m</t>
+          <t>2d 9h 16m</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2796,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>3d 4h 49m</t>
+          <t>2d 20h 22m</t>
         </is>
       </c>
     </row>
@@ -2543,10 +2837,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2651,10 +2945,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3078,7 +3372,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -3145,14 +3439,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
           <t>28 Sep 2026 07:25:28 AM</t>
@@ -3176,6 +3470,73 @@
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t>1d 3h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1349403</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Chausara Rai</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00:23 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:53:58 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00:32 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2563,10 +2563,8 @@
           <t>Chausara Rai</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9849445856</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9849445856</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2601,10 +2599,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.73813</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.73813</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2656,48 +2652,250 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L18-4</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.35905</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.35905</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 6m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:03 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2723,7 +2921,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2751,7 +2949,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2772,7 +2970,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3704,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2901,6 +2901,109 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:23 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2949,7 +3052,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2970,7 +3073,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3004,6 +3004,416 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348307</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Dada gaun view resort</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Dada gaun view resort</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9863037399</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:36:54 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9803694263</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:36:54 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:33:43 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Chundevi - Western restaurant M6WX+JC6 Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>11:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>A08-CDB4</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350224</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Anil Balami</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Anil Balami</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9803843277</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:16:57 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9803843277</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:16:57 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:43:55 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.71434</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>kathmandu, Swoyambhu Circle Road, near at Swoyambhu Circle Road, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>balamianil2001@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>06:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.28763</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3015,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3024,7 +3434,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3052,7 +3462,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3062,7 +3472,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -3073,7 +3483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3495,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2d 9h 16m</t>
+          <t>2d 3h 22m</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3507,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 20h 22m</t>
+          <t>2d 11h 42m</t>
         </is>
       </c>
     </row>
@@ -3138,10 +3548,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -3246,10 +3656,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3841,6 +4251,140 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348307</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Dada gaun view resort</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:36:54 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:36:54 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:33:43 AM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350224</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Anil Balami</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:16:57 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:16:57 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:43:55 AM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -517,13 +517,13 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -3071,10 +3071,8 @@
           <t>Dada gaun view resort</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9863037399</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9863037399</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3160,10 +3158,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3174,7 +3170,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3270,10 +3266,8 @@
           <t>Anil Balami</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9803843277</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9803843277</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3308,10 +3302,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.71434</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.71434</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3367,50 +3359,1272 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.28763</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.28762999999999</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>20h 26m</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>20h 26m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348787</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 07:09:52 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:50:06 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:29:49 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 19m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 39m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350274</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Jitendra kumar Jha</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Jitendra kumar Jha</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9860441314</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25:30 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9842608686</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:40:48 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25:30 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.68976</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>GEMS School - Higher secondary school Dhapakhel Rd, Lalitpur, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>jitendraphyhio05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>05:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB483</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.3443</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>19h 44m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350629</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Sambhu Shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Sambhu Shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9803179729</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:20 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803179729</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:17:56 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:20 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>S.S. college - College Q977+VRC Budhanilkantha 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>9803179729@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>02:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB532</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>16h 32m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>iptv not working</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347929</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9841059227</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841059227</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:01:25 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Swayamvu dallu, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>abcdef@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>11:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB255</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>iptv not working</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347929</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841059227</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841059227</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:01:25 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Swayamvu dallu, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>abcdef@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB255</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349734</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Shikhar Shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Shikhar Shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9849784121</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:49:02 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9849784121</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Mount Glory English Boarding High School - High school P74X+67M Jiwan Smriti Marg Kathmandu 44600, B</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>9849784121@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>10:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB414E</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3425,7 +4639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3462,7 +4676,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -3472,7 +4686,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -3483,7 +4697,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +4709,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2d 3h 22m</t>
+          <t>1d 7h 37m</t>
         </is>
       </c>
     </row>
@@ -3507,7 +4721,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 11h 42m</t>
+          <t>2d 1h 13m</t>
         </is>
       </c>
     </row>
@@ -3548,10 +4762,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -3566,14 +4780,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -3584,14 +4798,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3656,10 +4870,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3702,10 +4916,10 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -3748,14 +4962,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -4284,7 +5498,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4351,14 +5565,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>28 Sep 2026 03:16:57 PM</t>
@@ -4382,6 +5596,341 @@
       <c r="M33" s="5" t="inlineStr">
         <is>
           <t>20h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350274</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Jitendra kumar Jha</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25:30 AM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:40:48 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25:30 AM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>19h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350629</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Sambhu Shrestha</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:20 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:17:56 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:20 AM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>16h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347929</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:01:25 AM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1347929</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:01:25 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349734</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Shikhar Shrestha</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:49:02 AM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -3469,10 +3469,8 @@
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3558,10 +3556,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -3572,7 +3568,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -3668,10 +3664,8 @@
           <t>Jitendra kumar Jha</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9860441314</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9860441314</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3700,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.68976</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.68976</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -3765,25 +3757,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB483</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.3443</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.3443</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -3879,10 +3867,8 @@
           <t>Sambhu Shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9803179729</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9803179729</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -3954,10 +3940,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -3976,10 +3960,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -3990,7 +3972,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4086,10 +4068,8 @@
           <t>Hom ghale</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9841059227</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9841059227</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4179,10 +4159,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4193,7 +4171,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4289,10 +4267,8 @@
           <t>Hom ghale</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841059227</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841059227</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4382,10 +4358,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4396,7 +4370,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4492,10 +4466,8 @@
           <t>Shikhar Shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9849784121</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9849784121</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4585,10 +4557,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -4599,32 +4569,454 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1d 14m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.69473</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Melisa marg,Khadka Goun ,Oppoite way MK motorcycle workshop,Purano naikap,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>hemantshrestha1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>07:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB592</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.26357</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.69473</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Melisa marg,Khadka Goun ,Oppoite way MK motorcycle workshop,Purano naikap,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>hemantshrestha1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>07:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB592</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.26357</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4639,7 +5031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4676,7 +5068,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4686,7 +5078,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4697,7 +5089,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -4709,7 +5101,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 7h 37m</t>
+          <t>1d 6h 16m</t>
         </is>
       </c>
     </row>
@@ -4721,7 +5113,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 13m</t>
+          <t>1d 21h 31m</t>
         </is>
       </c>
     </row>
@@ -4762,10 +5154,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -4870,10 +5262,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -5632,7 +6024,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -5699,7 +6091,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -5766,7 +6158,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -5833,7 +6225,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -5900,14 +6292,14 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 11:49:02 AM</t>
@@ -5931,6 +6323,140 @@
       <c r="M38" s="3" t="inlineStr">
         <is>
           <t>1d 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -521,10 +521,10 @@
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -4665,10 +4665,8 @@
           <t>Hemant Shrestha</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9860298562</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9860298562</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -4703,10 +4701,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.69473</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.69473</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -4762,25 +4758,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB592</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.26357</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.26357</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -4876,10 +4868,8 @@
           <t>Hemant Shrestha</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9860298562</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9860298562</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -4914,10 +4904,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.69473</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.69473</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -4973,50 +4961,890 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB592</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.26357</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.26357</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>21h 28m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>21h 28m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351251</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Prabuddha Tuladhar</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Prabuddha Tuladhar</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9818051659</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9818051659</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:46:16 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.706385</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Chhauni,near Bella Pre School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>peashun@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>00:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.295835</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348585</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Achalshail Khadka</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Achalshail Khadka</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9848581014</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23:23 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9848581014</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:36:18 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23:23 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.67958</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Dharmasthal marg, Near Deepika School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>hkhadka317@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>12:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.34365</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 47m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348423</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:01:08 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:01:08 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:26:53 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Shree Manohar Secondary School - Community school P8P9+XPM Tokha 44600, , ,</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>kunwarprem849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L55-5</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 25m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 25m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349846</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Yangu Tamang</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Yangu Tamang</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9840602966</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:24:54 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04: 29:00 PM</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9847788551</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:29:19 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:25:14 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.744813</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Fluorescent secondary school, Baniyatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>yangutamang5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr">
+        <is>
+          <t>13:57 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.317203</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>23h 55m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5068,7 +5896,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -5078,7 +5906,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -5089,7 +5917,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5929,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 16m</t>
+          <t>1d 2h 42m</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5941,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 31m</t>
+          <t>1d 18h 50m</t>
         </is>
       </c>
     </row>
@@ -5154,14 +5982,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -5186,113 +6014,108 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -5304,18 +6127,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -5327,14 +6150,14 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -5345,259 +6168,171 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342919</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Mission shrestha</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-No internet connection on STB</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>6d 14h 15m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>6d 15h 25m</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5607,17 +6342,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -5627,64 +6362,64 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -5694,54 +6429,54 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5761,54 +6496,54 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -5828,22 +6563,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5853,19 +6588,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5895,44 +6630,44 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -5947,12 +6682,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -5962,44 +6697,44 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6014,12 +6749,12 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -6029,44 +6764,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -6081,12 +6816,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -6096,54 +6831,54 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -6163,22 +6898,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -6188,29 +6923,29 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -6230,22 +6965,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -6255,29 +6990,29 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -6297,166 +7032,434 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>TKT1349734</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Shikhar Shrestha</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:49:02 AM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>TKT1350135</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Hemant Shrestha</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>21h 28m</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>21h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351251</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Prabuddha Tuladhar</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:46:16 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348585</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Achalshail Khadka</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23:23 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:36:18 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23:23 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 47m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -523,7 +523,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -5071,10 +5071,8 @@
           <t>Prabuddha Tuladhar</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9818051659</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9818051659</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5109,10 +5107,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.706385</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.706385</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5168,25 +5164,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.295835</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.295835</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5282,10 +5274,8 @@
           <t>Achalshail Khadka</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9848581014</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9848581014</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5320,10 +5310,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.67958</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.67958</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5379,25 +5367,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.34365</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.34365</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5493,10 +5477,8 @@
           <t>Prem Bahadur Kunwar</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841458042</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841458042</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5582,10 +5564,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -5596,7 +5576,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -5692,10 +5672,8 @@
           <t>Yangu Tamang</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9840602966</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9840602966</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5734,10 +5712,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.744813</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.744813</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -5775,10 +5751,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
@@ -5801,50 +5775,448 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.317203</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.31720300000001</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>23h 55m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349429</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Bishwokarma</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Bishwokarma</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9765209837</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36:23 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>CHB9765209837</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:14:16 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36:23 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>ktm budhanilkantha jay baglug kalika sun chandi pasal, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>bk95@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>12:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L29-2</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>23h 55m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW29" s="3" t="inlineStr">
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 22m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340727</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:43:52 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:34:36 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Height Micro Station - Bus station Kathmandu 44600 - Kathmandu Metropolitan, Kathmandu, Bagma</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>00:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1h 50m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>8d 15h 40m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -5859,12 +6231,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -5896,7 +6268,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -5906,7 +6278,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5917,7 +6289,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -5929,7 +6301,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 42m</t>
+          <t>23h 59m</t>
         </is>
       </c>
     </row>
@@ -5941,7 +6313,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 50m</t>
+          <t>2d 2h 42m</t>
         </is>
       </c>
     </row>
@@ -5982,182 +6354,177 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>91.7%</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -6173,300 +6540,212 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342919</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Mission shrestha</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-No internet connection on STB</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>6d 14h 15m</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>6d 15h 25m</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -6476,17 +6755,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -6496,64 +6775,64 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6563,54 +6842,54 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -6630,54 +6909,54 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -6697,22 +6976,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -6722,19 +7001,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -6764,44 +7043,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -6816,12 +7095,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -6831,44 +7110,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6883,12 +7162,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -6898,44 +7177,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -6950,12 +7229,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -6965,54 +7244,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -7032,22 +7311,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -7057,29 +7336,29 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -7099,22 +7378,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -7124,29 +7403,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7166,64 +7445,64 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7233,44 +7512,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1349734</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Shikhar Shrestha</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7285,12 +7564,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -7300,44 +7579,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:49:02 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>28 Sep 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1351251</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Prabuddha Tuladhar</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7352,114 +7631,382 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:46:16 AM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351251</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Prabuddha Tuladhar</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:46:16 AM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>TKT1348585</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Achalshail Khadka</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>27 Sep 2026 03:36:18 PM</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>1d 20h 47m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1349429</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Sunil Bishwokarma</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36:23 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:14:16 AM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36:23 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>1d 3h 22m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340727</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:43:52 AM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:34:36 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>1h 50m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>8d 15h 40m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5885,10 +5885,8 @@
           <t>Sunil Bishwokarma</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9765209837</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9765209837</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -5978,10 +5976,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -5992,7 +5988,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6088,10 +6084,8 @@
           <t>Kamala gharti magar</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9860205079</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9860205079</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6177,10 +6171,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6191,7 +6183,7 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6240,7 +6232,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7909,7 +7901,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -7976,7 +7968,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6212,6 +6212,221 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350683</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Tek Bahadur Budha Magar</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Tek Bahadur Budha Magar</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9851192186</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9851192186</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:42 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.742863</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>????? ???, Kathmandu 44600 Near By Southwestern State College, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>motherisgod60@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>03:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L21-5</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.325422</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>17h 2m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6223,7 +6438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6232,7 +6447,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6260,7 +6475,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -6270,7 +6485,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6281,7 +6496,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6508,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>23h 59m</t>
+          <t>22h 47m</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6520,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 42m</t>
+          <t>2d 1h 1m</t>
         </is>
       </c>
     </row>
@@ -6346,14 +6561,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -6490,14 +6705,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>12</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -8002,6 +8217,73 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350683</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Tek Bahadur Budha Magar</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:42 PM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>17h 2m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6279,10 +6279,8 @@
           <t>Tek Bahadur Budha Magar</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9851192186</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9851192186</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6317,10 +6315,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.742863</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.742863</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6358,10 +6354,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH32" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH32" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
@@ -6380,48 +6374,251 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L21-5</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.325422</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.325422</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>17h 2m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>17h 2m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348342</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Niroj Bhakta</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Niroj Bhakta</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9841857813</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9841857813</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:20:44 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.711324</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila, Nagarjun 44600, Near by Kimdoll and opposite to army camp , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>13:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB055</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.286077</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6438,7 +6635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6475,7 +6672,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6485,7 +6682,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -6496,7 +6693,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6705,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 47m</t>
+          <t>1d</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6717,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 1m</t>
+          <t>2d 59m</t>
         </is>
       </c>
     </row>
@@ -6561,14 +6758,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -6705,14 +6902,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>13</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -8250,14 +8447,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 01:11:52 PM</t>
@@ -8281,6 +8478,73 @@
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>17h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348342</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Niroj Bhakta</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:20:44 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6484,10 +6484,8 @@
           <t>Niroj Bhakta</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9841857813</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9841857813</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6522,10 +6520,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.711324</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.711324</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6577,50 +6573,448 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB055</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.286077</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.28607700000001</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>2d 20m</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>2d 20m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349975</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Chettri</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Chettri</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9766430374</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:36:48 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9866087127</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:29:48 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:36:48 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Dhapasi - 6, Woda Office Dhapasi - 6, Woda Office, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>chettrisudip731@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>10:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 7m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349776</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Yuken Chamling Rai</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Yuken Chamling Rai</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9765079317</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:33:34 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>KLK9765079317</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 11:55:33 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:33:34 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Khatri Gawn Hatti Gauda - Housing society Q84X+44Q Budhanilkantha 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>9765079317@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 38m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -6635,7 +7029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6672,7 +7066,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -6682,7 +7076,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6693,7 +7087,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -6705,7 +7099,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>22h 55m</t>
         </is>
       </c>
     </row>
@@ -6717,7 +7111,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 59m</t>
+          <t>1d 23h 51m</t>
         </is>
       </c>
     </row>
@@ -6758,14 +7152,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -6776,14 +7170,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6902,14 +7296,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -6939,12 +7333,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -6967,18 +7361,18 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6990,14 +7384,14 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -7008,215 +7402,171 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7226,17 +7576,17 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -7246,32 +7596,32 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7695,32 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -7380,64 +7730,64 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -7447,44 +7797,44 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7499,12 +7849,12 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -7514,44 +7864,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7566,12 +7916,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -7581,44 +7931,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7648,44 +7998,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7700,12 +8050,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7715,44 +8065,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7782,22 +8132,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -7807,29 +8157,29 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -7849,22 +8199,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7874,7 +8224,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
@@ -7916,7 +8266,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -7948,22 +8298,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -7988,39 +8338,39 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1349734</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Shikhar Shrestha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -8035,12 +8385,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -8050,32 +8400,32 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:49:02 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>28 Sep 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
@@ -8149,12 +8499,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1351251</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Prabuddha Tuladhar</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8169,12 +8519,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -8184,44 +8534,44 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:46:16 AM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1348585</t>
+          <t>TKT1351251</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Achalshail Khadka</t>
+          <t>Prabuddha Tuladhar</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8251,22 +8601,22 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 03:36:18 PM</t>
+          <t>29 Sep 2026 11:46:16 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -8276,29 +8626,29 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 47m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1349429</t>
+          <t>TKT1348585</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Sunil Bishwokarma</t>
+          <t>Achalshail Khadka</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8318,22 +8668,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 09:14:16 AM</t>
+          <t>27 Sep 2026 03:36:18 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -8343,39 +8693,39 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 22m</t>
+          <t>1d 20h 47m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1340727</t>
+          <t>TKT1349429</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Kamala gharti magar</t>
+          <t>Sunil Bishwokarma</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -8385,44 +8735,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:43:52 AM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:53:45 PM</t>
+          <t>28 Sep 2026 09:14:16 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:34:36 PM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>8d 15h 40m</t>
+          <t>1d 3h 22m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1350683</t>
+          <t>TKT1340727</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Tek Bahadur Budha Magar</t>
+          <t>Kamala gharti magar</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -8437,12 +8787,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -8452,99 +8802,233 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 10:43:52 AM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:42 PM</t>
+          <t>20 Sep 2026 08:53:45 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 12:34:36 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 50m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>17h 2m</t>
+          <t>8d 15h 40m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>TKT1350683</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Tek Bahadur Budha Magar</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:42 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>17h 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>TKT1348342</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Niroj Bhakta</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 01:20:44 PM</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>2d 20m</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr">
         <is>
           <t>2d 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349975</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Chettri</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:36:48 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:29:48 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:36:48 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>1d 7m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW35"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6683,10 +6683,8 @@
           <t>Shanta Chettri</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9766430374</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9766430374</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6776,10 +6774,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -6790,7 +6786,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6886,10 +6882,8 @@
           <t>Yuken Chamling Rai</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9765079317</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9765079317</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6975,10 +6969,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -6989,32 +6981,239 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 38m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 38m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:41 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349414</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Ajita Pokhrel</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Ajita Pokhrel</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9767478420</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:01:24 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9851116870</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:01:24 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:41:32 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.69699</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki kasthamandap college - -(-)-Lead, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>pokhrelajita@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.28057</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7237,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7066,7 +7265,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -7087,7 +7286,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -7152,14 +7351,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>88.2%</t>
         </is>
       </c>
     </row>
@@ -7296,14 +7495,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>15</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>88.2%</t>
         </is>
       </c>
     </row>
@@ -8998,7 +9197,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7077,10 +7077,8 @@
           <t>Ajita Pokhrel</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9767478420</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9767478420</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7115,10 +7113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.69699</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.69699</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7170,48 +7166,653 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.28057</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.28057</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 40m</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 40m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348323</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>KOMA. Digital Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>KOMA. Digital Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9841504466</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:53:23 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9841504466</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:47:06 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:53:23 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>SubidhaNagar Tinkune - Fast food restaurant M8MW+5MX Pushpa Marg Kathmandu 44600, Kathmandu, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>shrestha.nirjal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>13:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 6m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>ONU Replacement</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348443</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Pandit</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Pandit</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9805193735</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:50:41 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>CHB9805193736</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:10:40 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:50:41 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>baneshwor, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>abcde@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>13:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 40m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:51 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351041</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Niraj kami</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Niraj kami</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9848502660</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9848502660</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:49:29 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Twenty Forty - Restaurant P82Q+GXJ Main Road Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>nirajankami2300@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>03:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L9-6</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7228,7 +7829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7237,7 +7838,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7265,7 +7866,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -7275,7 +7876,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -7286,7 +7887,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7899,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22h 55m</t>
+          <t>20h 10m</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7911,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 51m</t>
+          <t>1d 22h 8m</t>
         </is>
       </c>
     </row>
@@ -7351,14 +7952,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
     </row>
@@ -7495,26 +8096,26 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>15</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -7537,30 +8138,30 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -7583,18 +8184,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -7606,14 +8207,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -7624,215 +8225,171 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -7842,17 +8399,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -7862,32 +8419,32 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
@@ -7961,32 +8518,32 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -7996,64 +8553,64 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -8063,44 +8620,44 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8115,12 +8672,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -8130,44 +8687,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -8182,12 +8739,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -8197,44 +8754,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8264,44 +8821,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -8316,12 +8873,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -8331,44 +8888,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8398,22 +8955,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -8423,29 +8980,29 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -8465,22 +9022,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -8490,7 +9047,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
@@ -8532,7 +9089,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -8564,22 +9121,22 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -8604,39 +9161,39 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1349734</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Shikhar Shrestha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8651,12 +9208,12 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -8666,32 +9223,32 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:49:02 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>28 Sep 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
@@ -8765,12 +9322,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1351251</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Prabuddha Tuladhar</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8785,12 +9342,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -8800,44 +9357,44 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:46:16 AM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1348585</t>
+          <t>TKT1351251</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Achalshail Khadka</t>
+          <t>Prabuddha Tuladhar</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8867,22 +9424,22 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 03:36:18 PM</t>
+          <t>29 Sep 2026 11:46:16 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
@@ -8892,29 +9449,29 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 47m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1349429</t>
+          <t>TKT1348585</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Sunil Bishwokarma</t>
+          <t>Achalshail Khadka</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -8934,22 +9491,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 09:14:16 AM</t>
+          <t>27 Sep 2026 03:36:18 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -8959,39 +9516,39 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 22m</t>
+          <t>1d 20h 47m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1340727</t>
+          <t>TKT1349429</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Kamala gharti magar</t>
+          <t>Sunil Bishwokarma</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -9001,44 +9558,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:43:52 AM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:53:45 PM</t>
+          <t>28 Sep 2026 09:14:16 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:34:36 PM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>8d 15h 40m</t>
+          <t>1d 3h 22m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1350683</t>
+          <t>TKT1340727</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Tek Bahadur Budha Magar</t>
+          <t>Kamala gharti magar</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -9053,12 +9610,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -9068,44 +9625,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 10:43:52 AM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:42 PM</t>
+          <t>20 Sep 2026 08:53:45 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 12:34:36 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 50m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>17h 2m</t>
+          <t>8d 15h 40m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1348342</t>
+          <t>TKT1350683</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Niroj Bhakta</t>
+          <t>Tek Bahadur Budha Magar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -9120,12 +9677,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -9135,99 +9692,367 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>28 Sep 2026 08:09:42 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:20:44 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>17h 2m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>TKT1348342</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Niroj Bhakta</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:20:44 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>TKT1349975</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Shanta Chettri</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>28 Sep 2026 01:29:48 PM</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>1d 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348323</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>KOMA. Digital Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:53:23 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:47:06 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:53:23 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1348443</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Ajay Pandit</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:50:41 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:10:40 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:50:41 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 40m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351041</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Niraj kami</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:49:29 AM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7276,10 +7276,8 @@
           <t>KOMA. Digital Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9841504466</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9841504466</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7369,10 +7367,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -7383,7 +7379,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7479,10 +7475,8 @@
           <t>Ajay Pandit</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9805193735</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9805193735</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7572,10 +7566,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -7586,7 +7578,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7682,10 +7674,8 @@
           <t>Niraj kami</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9848502660</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9848502660</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7775,10 +7765,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -7789,7 +7777,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
@@ -7838,7 +7826,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9888,7 +9876,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -9955,7 +9943,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -10022,7 +10010,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7806,6 +7806,416 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:30 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348509</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Chiya Mantralaya</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Chiya Mantralaya</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9851253424</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:30:53 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851253424</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:49:19 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:30:53 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Mahadevstan janta sadak , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>Chiyamatralaya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>14:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB603</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 41m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:27 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341368</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bahadur Kuwar</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bahadur Kuwar</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9808622250</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:27:50 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9851241939</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:55:53 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:27:50 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.744472</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>New Castle Secondary School P8WP+J9H, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>22:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L11-5</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.33042</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>8d 31m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7817,7 +8227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7826,7 +8236,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7854,7 +8264,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -7864,7 +8274,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -7875,7 +8285,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -7887,7 +8297,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>20h 10m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
@@ -7899,7 +8309,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 8m</t>
+          <t>2d 3h 37m</t>
         </is>
       </c>
     </row>
@@ -7940,14 +8350,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -8084,14 +8494,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.5%</t>
         </is>
       </c>
     </row>
@@ -10044,6 +10454,140 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1348509</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Chiya Mantralaya</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:30:53 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:49:19 PM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:30:53 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 41m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341368</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bahadur Kuwar</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:27:50 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:55:53 PM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:27:50 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>8d 31m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW41"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7873,10 +7873,8 @@
           <t>Chiya Mantralaya</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9851253424</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9851253424</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7966,10 +7964,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -7980,7 +7976,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8076,10 +8072,8 @@
           <t>Ram Bahadur Kuwar</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9808622250</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9808622250</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8114,10 +8108,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.744472</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.744472</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -8169,48 +8161,255 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L11-5</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.33042</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.33042</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>8d 31m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>8d 31m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:34 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349332</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Khadka</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Khadka</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9851074853</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:17 AM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9851074853</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:08:08 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:34:36 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.69419</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Infront of NMB bank building , the building where  Mega Bank is located, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>bishnuitis@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>14:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>CDB026</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.2845</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 25m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8227,7 +8426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8264,7 +8463,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -8274,7 +8473,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -8285,7 +8484,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8496,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>19h 5m</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8508,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 3h 37m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
@@ -8350,14 +8549,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.3%</t>
         </is>
       </c>
     </row>
@@ -8494,14 +8693,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10686,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -10554,14 +10753,14 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 02:27:50 PM</t>
@@ -10585,6 +10784,73 @@
       <c r="M58" s="3" t="inlineStr">
         <is>
           <t>8d 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1349332</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Khadka</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:17 AM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:08:08 AM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:34:36 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 25m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8271,10 +8271,8 @@
           <t>Bishnu Kumar Khadka</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9851074853</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9851074853</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8309,10 +8307,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.69419</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.69419</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8368,48 +8364,863 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>CDB026</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.2845</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.28449999999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 25m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 25m</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 26m</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:49 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347959</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Susila Shah</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Susila Shah</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9822854396</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:49:53 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9822854396</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:22:32 AM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:49:53 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.75125</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Yoga Teacher Training and Retreat Center Goldhunga -5, Kathmandu 44600, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>14:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L60-2</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.286398</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 27m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:51 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Client is asking for technical team</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349795</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9823765832</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849220717</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:05:36 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Pako Newroad Tamrakar Complex Near By Tamrakar Complex - Pako Newroad Tamrakar Complex Near By Tamra</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>12:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB161A</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:48 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9708030031</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:41:13 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708030031</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:48:50 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Bhotebahal Futsal - Futsal court M8W6+G76 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>9708030031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB015</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>8d 3h 31m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="AA46" s="3" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AC46" s="3" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr"/>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr"/>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr"/>
+      <c r="AM46" s="3" t="inlineStr"/>
+      <c r="AN46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -8426,7 +9237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8463,7 +9274,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -8473,7 +9284,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -8484,7 +9295,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -8496,7 +9307,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>19h 5m</t>
+          <t>17h 49m</t>
         </is>
       </c>
     </row>
@@ -8508,7 +9319,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>2d 2h 9m</t>
         </is>
       </c>
     </row>
@@ -8549,14 +9360,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>88.0%</t>
         </is>
       </c>
     </row>
@@ -8585,14 +9396,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -8693,14 +9504,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -8785,14 +9596,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -10820,14 +11631,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>28 Sep 2026 08:09:17 AM</t>
@@ -10851,6 +11662,140 @@
       <c r="M59" s="5" t="inlineStr">
         <is>
           <t>1d 6h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347959</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Susila Shah</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:49:53 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:22:32 AM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:49:53 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1349795</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:05:36 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8474,10 +8474,8 @@
           <t>Susila Shah</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9822854396</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9822854396</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8512,10 +8510,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.75125</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.75125</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8567,25 +8563,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L60-2</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.286398</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.28639800000001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -8671,20 +8663,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9823765832</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9823765832</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8756,10 +8742,8 @@
           <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="AH44" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH44" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
@@ -8778,10 +8762,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
@@ -8792,7 +8774,7 @@
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8888,10 +8870,8 @@
           <t>Sirjana Gurung</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9708030031</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9708030031</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8977,10 +8957,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -8991,7 +8969,7 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9246,7 +9224,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11698,7 +11676,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -11765,7 +11743,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW47"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9204,6 +9204,315 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr"/>
+      <c r="AN48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr"/>
+      <c r="V49" s="3" t="inlineStr"/>
+      <c r="W49" s="3" t="inlineStr"/>
+      <c r="X49" s="3" t="inlineStr"/>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr"/>
+      <c r="AA49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr"/>
+      <c r="AC49" s="3" t="inlineStr"/>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr"/>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr"/>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr"/>
+      <c r="AM49" s="3" t="inlineStr"/>
+      <c r="AN49" s="3" t="inlineStr"/>
+      <c r="AO49" s="3" t="inlineStr"/>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr"/>
+      <c r="AA50" s="3" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr"/>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr"/>
+      <c r="AM50" s="3" t="inlineStr"/>
+      <c r="AN50" s="3" t="inlineStr"/>
+      <c r="AO50" s="3" t="inlineStr"/>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9252,7 +9561,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9273,7 +9582,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9513,6 +9513,412 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350680</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Nikesh tamang</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Nikesh tamang</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9808993896</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9818747627</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:06:51 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>North valley school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr"/>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>05:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L1-6</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:35:03 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:35:03 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr"/>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 28m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9524,7 +9930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9533,7 +9939,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9561,7 +9967,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -9571,7 +9977,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -9582,7 +9988,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -9594,7 +10000,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 49m</t>
+          <t>17h 14m</t>
         </is>
       </c>
     </row>
@@ -9606,7 +10012,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 9m</t>
+          <t>2d 1h 9m</t>
         </is>
       </c>
     </row>
@@ -9647,14 +10053,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -9791,14 +10197,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -12086,6 +12492,73 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350680</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Nikesh tamang</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:06:51 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW52"/>
+  <dimension ref="A1:AW53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9580,10 +9580,8 @@
           <t>Nikesh tamang</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9808993896</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9808993896</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -9669,10 +9667,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -9683,7 +9679,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -9779,10 +9775,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -9817,10 +9811,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -9872,48 +9864,255 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 28m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>8d 1h 28m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:51 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351404</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:51:52 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>02:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9930,7 +10129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9967,7 +10166,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -9977,7 +10176,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -9988,7 +10187,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10199,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 14m</t>
+          <t>16h 47m</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10211,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 9m</t>
+          <t>1d 23h 42m</t>
         </is>
       </c>
     </row>
@@ -10053,14 +10252,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -10197,14 +10396,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -12525,14 +12724,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 03:38:55 PM</t>
@@ -12556,6 +12755,73 @@
       <c r="M62" s="3" t="inlineStr">
         <is>
           <t>19h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351404</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:51:52 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW53"/>
+  <dimension ref="A1:AW57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -9974,10 +9974,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10012,10 +10010,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -10071,48 +10067,864 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS53" s="3" t="inlineStr">
-        <is>
-          <t>2h 33m</t>
-        </is>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>2h 33m</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV53" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:16 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347144</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9867339967</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:16:22 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>KLK9867339967</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:50:56 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:16:22 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Kirtipur Hospital, Kirtipur Ring Rd, Kathmandu 44618, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>apyfx.np@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>CDB191</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 25m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:11 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349548</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Hari Saran Karki</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Hari Saran Karki</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9841720683</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:11:14 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9841720683</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 10:07:13 AM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:11:14 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.70144</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Nearby Sankata Mandir, Shree Ganesh Mandir and Close to Niyetar Sahakari, Te Bahal, Kathmandu, Bagma</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>bcs2039@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>16:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.31281</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 4m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:09 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>slow Internet</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348195</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:09:31 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:21:12 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:09:31 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr"/>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Clicked Location 27.70858, 85.33194 Nearest: CDB436 (45m Road) Map: CG Putalisadak, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr"/>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB256</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr"/>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 48m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:07 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351280</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9762414088</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:28 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>mizu_fttx</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:14 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:07:08 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.694534</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Complex, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>manoj.pradhan@rameshcorp.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB175</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.311309</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -10129,7 +10941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10166,7 +10978,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -10176,7 +10988,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -10187,7 +10999,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -10199,7 +11011,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 47m</t>
+          <t>16h 16m</t>
         </is>
       </c>
     </row>
@@ -10211,7 +11023,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 42m</t>
+          <t>1d 23h 10m</t>
         </is>
       </c>
     </row>
@@ -10252,14 +11064,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -10324,14 +11136,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -10396,14 +11208,14 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -10576,187 +11388,143 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -10766,17 +11534,17 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -10786,32 +11554,32 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
@@ -10885,32 +11653,32 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -10920,64 +11688,64 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -10987,44 +11755,44 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -11039,12 +11807,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -11054,44 +11822,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -11106,12 +11874,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -11121,44 +11889,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -11188,44 +11956,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -11240,12 +12008,12 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -11255,44 +12023,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -11322,22 +12090,22 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -11347,29 +12115,29 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -11389,22 +12157,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -11414,7 +12182,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
@@ -11456,7 +12224,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -11488,22 +12256,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -11528,39 +12296,39 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1349734</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Shikhar Shrestha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -11575,12 +12343,12 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -11590,32 +12358,32 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:49:02 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>28 Sep 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
@@ -11689,12 +12457,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1351251</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Prabuddha Tuladhar</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -11709,12 +12477,12 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -11724,44 +12492,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:46:16 AM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1348585</t>
+          <t>TKT1351251</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Achalshail Khadka</t>
+          <t>Prabuddha Tuladhar</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -11791,22 +12559,22 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 03:36:18 PM</t>
+          <t>29 Sep 2026 11:46:16 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
@@ -11816,29 +12584,29 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 47m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1349429</t>
+          <t>TKT1348585</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Sunil Bishwokarma</t>
+          <t>Achalshail Khadka</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -11858,22 +12626,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 09:14:16 AM</t>
+          <t>27 Sep 2026 03:36:18 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -11883,39 +12651,39 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 22m</t>
+          <t>1d 20h 47m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1340727</t>
+          <t>TKT1349429</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Kamala gharti magar</t>
+          <t>Sunil Bishwokarma</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -11925,44 +12693,44 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:43:52 AM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:53:45 PM</t>
+          <t>28 Sep 2026 09:14:16 AM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:34:36 PM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>8d 15h 40m</t>
+          <t>1d 3h 22m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1350683</t>
+          <t>TKT1340727</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Tek Bahadur Budha Magar</t>
+          <t>Kamala gharti magar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -11977,12 +12745,12 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -11992,44 +12760,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 10:43:52 AM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:42 PM</t>
+          <t>20 Sep 2026 08:53:45 PM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 12:34:36 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 50m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>17h 2m</t>
+          <t>8d 15h 40m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1348342</t>
+          <t>TKT1350683</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Niroj Bhakta</t>
+          <t>Tek Bahadur Budha Magar</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12044,12 +12812,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -12059,44 +12827,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>28 Sep 2026 08:09:42 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:20:44 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>17h 2m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1349975</t>
+          <t>TKT1348342</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Shanta Chettri</t>
+          <t>Niroj Bhakta</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -12111,12 +12879,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -12126,44 +12894,44 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:36:48 PM</t>
+          <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 01:29:48 PM</t>
+          <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:36:48 PM</t>
+          <t>29 Sep 2026 01:20:44 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>1d 7m</t>
+          <t>2d 20m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1348323</t>
+          <t>TKT1349975</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>KOMA. Digital Pvt. Ltd</t>
+          <t>Shanta Chettri</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12193,22 +12961,22 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:53:23 PM</t>
+          <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:47:06 PM</t>
+          <t>28 Sep 2026 01:29:48 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:53:23 PM</t>
+          <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -12218,19 +12986,19 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 6m</t>
+          <t>1d 7m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1348443</t>
+          <t>TKT1348323</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Ajay Pandit</t>
+          <t>KOMA. Digital Pvt. Ltd</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -12240,7 +13008,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -12260,22 +13028,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:50:41 PM</t>
+          <t>29 Sep 2026 01:53:23 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 02:10:40 PM</t>
+          <t>27 Sep 2026 12:47:06 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:50:41 PM</t>
+          <t>29 Sep 2026 01:53:23 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -12285,19 +13053,19 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 40m</t>
+          <t>2d 1h 6m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1351041</t>
+          <t>TKT1348443</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Niraj kami</t>
+          <t>Ajay Pandit</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12307,7 +13075,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -12327,22 +13095,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:51:30 PM</t>
+          <t>29 Sep 2026 01:50:41 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 09:49:29 AM</t>
+          <t>27 Sep 2026 02:10:40 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:51:30 PM</t>
+          <t>29 Sep 2026 01:50:41 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -12352,19 +13120,19 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>4h 2m</t>
+          <t>1d 23h 40m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1348509</t>
+          <t>TKT1351041</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Chiya Mantralaya</t>
+          <t>Niraj kami</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -12394,22 +13162,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:30:53 PM</t>
+          <t>29 Sep 2026 01:51:30 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 02:49:19 PM</t>
+          <t>29 Sep 2026 09:49:29 AM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:30:53 PM</t>
+          <t>29 Sep 2026 01:51:30 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -12419,19 +13187,19 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 41m</t>
+          <t>4h 2m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1341368</t>
+          <t>TKT1348509</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Ram Bahadur Kuwar</t>
+          <t>Chiya Mantralaya</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -12461,22 +13229,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:27:50 PM</t>
+          <t>29 Sep 2026 02:30:53 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:55:53 PM</t>
+          <t>27 Sep 2026 02:49:19 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:27:50 PM</t>
+          <t>29 Sep 2026 02:30:53 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -12486,19 +13254,19 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>8d 31m</t>
+          <t>1d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1349332</t>
+          <t>TKT1341368</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Bishnu Kumar Khadka</t>
+          <t>Ram Bahadur Kuwar</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -12513,12 +13281,12 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -12528,44 +13296,44 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:17 AM</t>
+          <t>29 Sep 2026 02:27:50 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:08:08 AM</t>
+          <t>21 Sep 2026 01:55:53 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:34:36 PM</t>
+          <t>29 Sep 2026 02:27:50 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 26m</t>
+          <t>8d 31m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1347959</t>
+          <t>TKT1349332</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Susila Shah</t>
+          <t>Bishnu Kumar Khadka</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -12580,12 +13348,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -12595,54 +13363,54 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:49:53 PM</t>
+          <t>28 Sep 2026 08:09:17 AM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:22:32 AM</t>
+          <t>28 Sep 2026 08:08:08 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:49:53 PM</t>
+          <t>29 Sep 2026 02:34:36 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 6h 25m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 27m</t>
+          <t>1d 6h 26m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1349795</t>
+          <t>TKT1347959</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Maniraj Singh Maharjan</t>
+          <t>Susila Shah</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -12662,22 +13430,22 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:51:12 PM</t>
+          <t>29 Sep 2026 02:49:53 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 12:05:36 PM</t>
+          <t>27 Sep 2026 09:22:32 AM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:51:12 PM</t>
+          <t>29 Sep 2026 02:49:53 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -12687,29 +13455,29 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 45m</t>
+          <t>2d 5h 27m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1350680</t>
+          <t>TKT1349795</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Nikesh tamang</t>
+          <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -12729,22 +13497,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:38:55 PM</t>
+          <t>29 Sep 2026 02:51:12 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:06:51 PM</t>
+          <t>28 Sep 2026 12:05:36 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:38:55 PM</t>
+          <t>29 Sep 2026 02:51:12 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -12754,74 +13522,208 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>1d 2h 45m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>TKT1350680</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Nikesh tamang</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:06:51 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
           <t>TKT1351404</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 01:18:14 PM</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 01:18:14 PM</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 03:51:52 PM</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>2h 33m</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr">
         <is>
           <t>2h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>TKT1349548</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Hari Saran Karki</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:11:14 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 10:07:13 AM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:11:14 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 4m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW57"/>
+  <dimension ref="A1:AW61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10177,10 +10177,8 @@
           <t>Anil Pandey</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9867339967</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9867339967</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -10266,10 +10264,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -10280,7 +10276,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -10376,10 +10372,8 @@
           <t>Hari Saran Karki</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9841720683</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9841720683</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -10414,10 +10408,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.70144</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.70144</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -10455,10 +10447,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH55" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH55" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
@@ -10477,25 +10467,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.31281</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.31281</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -10591,10 +10577,8 @@
           <t>Anuj  Kuwar</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9860614634</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9860614634</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -10662,10 +10646,8 @@
           <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
-      <c r="AH56" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH56" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI56" s="3" t="inlineStr"/>
       <c r="AJ56" s="3" t="inlineStr"/>
@@ -10680,10 +10662,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
@@ -10694,7 +10674,7 @@
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -10790,10 +10770,8 @@
           <t>Ramjanaki Hydropower Pvt.Ltd.</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9762414088</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9762414088</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -10828,10 +10806,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.694534</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.694534</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -10883,48 +10859,884 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>CDB175</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.311309</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.31130899999999</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>4h 6m</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>4h 6m</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV57" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:17 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348787</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:17:54 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:50:06 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:17:54 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>16:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 27m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:27 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>5g not working</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350460</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 05:16:24 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:59:00 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:27:32 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.676037</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Basic Learning English Secondary School - School M6GW+HCQ Chandragiri 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>sontoshashkya01@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>09:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.247317</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:25 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>5g not working</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350460</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 05:16:24 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:59:00 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:27:32 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>27.676037</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Basic Learning English Secondary School - School M6GW+HCQ Chandragiri 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>sontoshashkya01@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>09:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>85.247317</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346312</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Basanta Kunwar</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Basanta Kunwar</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9861900763</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:11:18 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9861900763</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:11:18 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:25:31 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr"/>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>27.688232, 85.271605, Sundarban School Of Science - School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>reetukuor22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>06:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr"/>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>4d 14m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>4d 14m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -10941,7 +11753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10978,7 +11790,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -10988,7 +11800,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -10999,7 +11811,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11823,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 16m</t>
+          <t>18h 22m</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11835,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 10m</t>
+          <t>1d 23h 11m</t>
         </is>
       </c>
     </row>
@@ -11064,14 +11876,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -11136,14 +11948,14 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -11204,18 +12016,18 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -11227,30 +12039,30 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -11273,41 +12085,41 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -11319,18 +12131,18 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -11342,14 +12154,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -11360,35 +12172,35 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -11411,187 +12223,143 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -11601,17 +12369,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -11621,32 +12389,32 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
@@ -11720,32 +12488,32 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -11755,64 +12523,64 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -11822,44 +12590,44 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -11874,12 +12642,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -11889,44 +12657,44 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -11941,12 +12709,12 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -11956,44 +12724,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12023,44 +12791,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -12075,12 +12843,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -12090,44 +12858,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -12157,22 +12925,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -12182,29 +12950,29 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -12224,22 +12992,22 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -12249,7 +13017,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
@@ -12291,7 +13059,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -12323,22 +13091,22 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -12363,39 +13131,39 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1349734</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Shikhar Shrestha</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12410,12 +13178,12 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -12425,32 +13193,32 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:49:02 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>28 Sep 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
@@ -12524,12 +13292,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1351251</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Prabuddha Tuladhar</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12544,12 +13312,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -12559,44 +13327,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:46:16 AM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1348585</t>
+          <t>TKT1351251</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Achalshail Khadka</t>
+          <t>Prabuddha Tuladhar</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -12626,22 +13394,22 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 03:36:18 PM</t>
+          <t>29 Sep 2026 11:46:16 AM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -12651,29 +13419,29 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>1d 20h 47m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1349429</t>
+          <t>TKT1348585</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Sunil Bishwokarma</t>
+          <t>Achalshail Khadka</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -12693,22 +13461,22 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 09:14:16 AM</t>
+          <t>27 Sep 2026 03:36:18 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
@@ -12718,39 +13486,39 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 22m</t>
+          <t>1d 20h 47m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1340727</t>
+          <t>TKT1349429</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Kamala gharti magar</t>
+          <t>Sunil Bishwokarma</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -12760,44 +13528,44 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:43:52 AM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:53:45 PM</t>
+          <t>28 Sep 2026 09:14:16 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:34:36 PM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>8d 15h 40m</t>
+          <t>1d 3h 22m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1350683</t>
+          <t>TKT1340727</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Tek Bahadur Budha Magar</t>
+          <t>Kamala gharti magar</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12812,12 +13580,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -12827,44 +13595,44 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 10:43:52 AM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:42 PM</t>
+          <t>20 Sep 2026 08:53:45 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 12:34:36 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 50m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>17h 2m</t>
+          <t>8d 15h 40m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1348342</t>
+          <t>TKT1350683</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Niroj Bhakta</t>
+          <t>Tek Bahadur Budha Magar</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -12879,12 +13647,12 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -12894,44 +13662,44 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>28 Sep 2026 08:09:42 PM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:20:44 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>17h 2m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1349975</t>
+          <t>TKT1348342</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Shanta Chettri</t>
+          <t>Niroj Bhakta</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12946,12 +13714,12 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -12961,44 +13729,44 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:36:48 PM</t>
+          <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 01:29:48 PM</t>
+          <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:36:48 PM</t>
+          <t>29 Sep 2026 01:20:44 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1d 7m</t>
+          <t>2d 20m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1348323</t>
+          <t>TKT1349975</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>KOMA. Digital Pvt. Ltd</t>
+          <t>Shanta Chettri</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -13028,22 +13796,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:53:23 PM</t>
+          <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:47:06 PM</t>
+          <t>28 Sep 2026 01:29:48 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:53:23 PM</t>
+          <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -13053,19 +13821,19 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2d 1h 6m</t>
+          <t>1d 7m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1348443</t>
+          <t>TKT1348323</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Ajay Pandit</t>
+          <t>KOMA. Digital Pvt. Ltd</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -13075,7 +13843,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -13095,22 +13863,22 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:50:41 PM</t>
+          <t>29 Sep 2026 01:53:23 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 02:10:40 PM</t>
+          <t>27 Sep 2026 12:47:06 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:50:41 PM</t>
+          <t>29 Sep 2026 01:53:23 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -13120,19 +13888,19 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 40m</t>
+          <t>2d 1h 6m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1351041</t>
+          <t>TKT1348443</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Niraj kami</t>
+          <t>Ajay Pandit</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -13142,7 +13910,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -13162,22 +13930,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:51:30 PM</t>
+          <t>29 Sep 2026 01:50:41 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 09:49:29 AM</t>
+          <t>27 Sep 2026 02:10:40 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:51:30 PM</t>
+          <t>29 Sep 2026 01:50:41 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -13187,19 +13955,19 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>4h 2m</t>
+          <t>1d 23h 40m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1348509</t>
+          <t>TKT1351041</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Chiya Mantralaya</t>
+          <t>Niraj kami</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -13229,22 +13997,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:30:53 PM</t>
+          <t>29 Sep 2026 01:51:30 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 02:49:19 PM</t>
+          <t>29 Sep 2026 09:49:29 AM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:30:53 PM</t>
+          <t>29 Sep 2026 01:51:30 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -13254,19 +14022,19 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 41m</t>
+          <t>4h 2m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1341368</t>
+          <t>TKT1348509</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Ram Bahadur Kuwar</t>
+          <t>Chiya Mantralaya</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -13296,22 +14064,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:27:50 PM</t>
+          <t>29 Sep 2026 02:30:53 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:55:53 PM</t>
+          <t>27 Sep 2026 02:49:19 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:27:50 PM</t>
+          <t>29 Sep 2026 02:30:53 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -13321,19 +14089,19 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>8d 31m</t>
+          <t>1d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1349332</t>
+          <t>TKT1341368</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Bishnu Kumar Khadka</t>
+          <t>Ram Bahadur Kuwar</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -13348,12 +14116,12 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -13363,44 +14131,44 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:17 AM</t>
+          <t>29 Sep 2026 02:27:50 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:08:08 AM</t>
+          <t>21 Sep 2026 01:55:53 PM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:34:36 PM</t>
+          <t>29 Sep 2026 02:27:50 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 26m</t>
+          <t>8d 31m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1347959</t>
+          <t>TKT1349332</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Susila Shah</t>
+          <t>Bishnu Kumar Khadka</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -13415,12 +14183,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -13430,54 +14198,54 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:49:53 PM</t>
+          <t>28 Sep 2026 08:09:17 AM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:22:32 AM</t>
+          <t>28 Sep 2026 08:08:08 AM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:49:53 PM</t>
+          <t>29 Sep 2026 02:34:36 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 6h 25m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>2d 5h 27m</t>
+          <t>1d 6h 26m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1349795</t>
+          <t>TKT1347959</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Maniraj Singh Maharjan</t>
+          <t>Susila Shah</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -13497,22 +14265,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:51:12 PM</t>
+          <t>29 Sep 2026 02:49:53 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 12:05:36 PM</t>
+          <t>27 Sep 2026 09:22:32 AM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:51:12 PM</t>
+          <t>29 Sep 2026 02:49:53 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -13522,29 +14290,29 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1d 2h 45m</t>
+          <t>2d 5h 27m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1350680</t>
+          <t>TKT1349795</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Nikesh tamang</t>
+          <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -13564,22 +14332,22 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:38:55 PM</t>
+          <t>29 Sep 2026 02:51:12 PM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:06:51 PM</t>
+          <t>28 Sep 2026 12:05:36 PM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:38:55 PM</t>
+          <t>29 Sep 2026 02:51:12 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -13589,19 +14357,19 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>1d 2h 45m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1351404</t>
+          <t>TKT1350680</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Nikesh tamang</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -13616,12 +14384,12 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -13631,99 +14399,434 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:18:14 PM</t>
+          <t>29 Sep 2026 03:38:55 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:18:14 PM</t>
+          <t>28 Sep 2026 08:06:51 PM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:51:52 PM</t>
+          <t>29 Sep 2026 03:38:55 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2h 33m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2h 33m</t>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>TKT1351404</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:51:52 PM</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
           <t>TKT1349548</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Hari Saran Karki</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 04:11:14 PM</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>28 Sep 2026 10:07:13 AM</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 04:11:14 PM</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>1d 6h 4m</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TKT1348787</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:17:54 PM</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:50:06 PM</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:17:54 PM</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>1d 22h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350460</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 05:16:24 PM</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:59:00 PM</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:27:32 PM</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350460</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 05:16:24 PM</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:59:00 PM</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:27:32 PM</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346312</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Basanta Kunwar</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:11:18 PM</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:11:18 PM</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:25:31 PM</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>4d 14m</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>4d 14m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10969,10 +10969,8 @@
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -11062,10 +11060,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -11076,7 +11072,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -11172,10 +11168,8 @@
           <t>santoshi shakya</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9825593167</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9825593167</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -11210,10 +11204,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.676037</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.676037</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -11251,10 +11243,8 @@
           <t>General Query &amp; Feedback</t>
         </is>
       </c>
-      <c r="AH59" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH59" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
@@ -11273,25 +11263,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.247317</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.247317</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -11387,10 +11373,8 @@
           <t>santoshi shakya</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9825593167</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9825593167</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -11425,10 +11409,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>27.676037</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>27.676037</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -11466,10 +11448,8 @@
           <t>General Query &amp; Feedback</t>
         </is>
       </c>
-      <c r="AH60" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH60" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
@@ -11488,25 +11468,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>85.247317</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>85.247317</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -11602,10 +11578,8 @@
           <t>Basanta Kunwar</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9861900763</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9861900763</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -11677,10 +11651,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH61" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH61" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
@@ -11699,10 +11671,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
@@ -11713,7 +11683,7 @@
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
@@ -11762,7 +11732,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -14595,7 +14565,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -14662,7 +14632,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -14729,7 +14699,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -14796,7 +14766,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW61"/>
+  <dimension ref="A1:AW68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
@@ -528,8 +528,8 @@
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="43" max="43"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11712,6 +11712,1491 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:52 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Router Adapter damage</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349489</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Mithilesh Thakur</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Mithilesh Thakur</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9807679964</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 10:01:37 AM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9807679964</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:40:11 AM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:52:31 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr">
+        <is>
+          <t>27.684118</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Armed Police Force Hospital Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr">
+        <is>
+          <t>mithileshthakur21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>16:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>CDB422</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>85.249251</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 50m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 12m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:50 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350899</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Sulaina Shahi</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Sulaina Shahi</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9840745095</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:53 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9843218118</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:40:54 AM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:53 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>27.679821</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Int'l Academy,M8JM+625, Bangalamukhi-Sankhamul Rd, Kathmandu ward no 31, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>shahisulaina999@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>06:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>85.332532</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>9h 9m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:01 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351481</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Punam Kumari Shrestha</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Punam Kumari Shrestha</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9841879407</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:01:53 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9851167300k</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:07:03 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:01:53 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.69045</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa ( Inside Ring Road ) Panchakumari Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>umeshpunam07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>CDB682</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.3063</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:37 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>no light on the router</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351387</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Thapa</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Thapa</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9816014031</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>CHB9816014031</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:09:37 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Mandikatar Heights - Lodge P8PX+J43 Mandikhata Rd Budhanilkantha 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>9816014031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>03:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>L55-5A</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr"/>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>3h 28m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:25 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>wif6</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351319</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Kalyan Adhikari</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Kalyan Adhikari</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9841960700</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841960700</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:17:31 PM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr"/>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>Saipal Academy Saipal Academy - College Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>9841960700@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>04:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>L11-5</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr"/>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:00 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347646</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:00:44 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 07:33:35 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:00:44 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.72209</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>Panchdhara Near Kamala beauty parlor , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr"/>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>17:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.27905</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri
+(29 Sep 2026 05:00:45 PM) :
+TKT1347646
+9818815777
+Sabin Shrestha
+MAC:900EB3C7ED48(new)
+MAC:D0765854CBEB(old)
+Note: user upgrade to WiFi 6 and sky com box doesn'''+'t support ethernet wire.
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri
+(29 Sep 2026 05:00:45 PM) :
+TKT1347646
+9818815777
+Sabin Shrestha
+MAC:900EB3C7ED48(new)
+MAC:D0765854CBEB(old)
+Note: user upgrade to WiFi 6 and sky com box doesn'''+'t support ethernet wire.
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 27m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351071</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Maya K.C</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Maya K.C</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9841069288</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:31:53 PM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9841069288</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:08:24 AM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:31:53 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>27.73591</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>Near to NCEB School (???? ???????? ?????? ??????? ?????) ,Kathmandu 44600 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>shishirkc332@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>06:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>85.28792</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 23m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11723,7 +13208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -11732,7 +13217,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11760,7 +13245,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -11770,7 +13255,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -11781,7 +13266,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -11793,7 +13278,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>18h 22m</t>
+          <t>16h 9m</t>
         </is>
       </c>
     </row>
@@ -11805,7 +13290,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 11m</t>
+          <t>1d 18h 34m</t>
         </is>
       </c>
     </row>
@@ -11846,14 +13331,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>84.2%</t>
         </is>
       </c>
     </row>
@@ -11864,14 +13349,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -11882,14 +13367,14 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -12013,14 +13498,14 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -12082,14 +13567,14 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -12151,10 +13636,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -14800,6 +16285,485 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>TKT1349489</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Mithilesh Thakur</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 10:01:37 AM</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:40:11 AM</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:52:31 PM</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>1d 6h 50m</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>1d 7h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350899</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Sulaina Shahi</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:53 PM</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:40:54 AM</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:53 PM</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>9h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351481</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Punam Kumari Shrestha</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:01:53 PM</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:07:03 PM</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:01:53 PM</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351387</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Thapa</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:09:37 PM</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>3h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351319</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Kalyan Adhikari</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:17:31 PM</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347646</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri
+(29 Sep 2026 05:00:45 PM) :
+TKT1347646
+9818815777
+Sabin Shrestha
+MAC:900EB3C7ED48(new)
+MAC:D0765854CBEB(old)
+Note: user upgrade to WiFi 6 and sky com box doesn'''+'t support ethernet wire.
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:00:44 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 07:33:35 PM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:00:44 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351071</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Maya K.C</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:31:53 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:08:24 AM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:31:53 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>6h 23m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW68"/>
+  <dimension ref="A1:AW72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11779,10 +11779,8 @@
           <t>Mithilesh Thakur</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9807679964</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9807679964</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -11817,10 +11815,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y62" s="3" t="inlineStr">
-        <is>
-          <t>27.684118</t>
-        </is>
+      <c r="Y62" s="3" t="n">
+        <v>27.684118</v>
       </c>
       <c r="Z62" s="3" t="inlineStr">
         <is>
@@ -11876,25 +11872,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
           <t>CDB422</t>
         </is>
       </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>85.249251</t>
-        </is>
+      <c r="AP62" s="3" t="n">
+        <v>85.249251</v>
       </c>
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
@@ -11990,10 +11982,8 @@
           <t>Sulaina Shahi</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9840745095</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9840745095</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -12028,10 +12018,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y63" s="3" t="inlineStr">
-        <is>
-          <t>27.679821</t>
-        </is>
+      <c r="Y63" s="3" t="n">
+        <v>27.679821</v>
       </c>
       <c r="Z63" s="3" t="inlineStr">
         <is>
@@ -12087,25 +12075,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="AP63" s="3" t="inlineStr">
-        <is>
-          <t>85.332532</t>
-        </is>
+      <c r="AP63" s="3" t="n">
+        <v>85.332532</v>
       </c>
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -12201,10 +12185,8 @@
           <t>Punam Kumari Shrestha</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9841879407</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9841879407</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -12239,10 +12221,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.69045</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.69045</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -12298,25 +12278,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>CDB682</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.3063</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.30629999999999</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
@@ -12412,10 +12388,8 @@
           <t>Ritika Thapa</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9816014031</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9816014031</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -12505,10 +12479,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -12519,7 +12491,7 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
@@ -12615,10 +12587,8 @@
           <t>Kalyan Adhikari</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9841960700</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9841960700</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -12708,10 +12678,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
@@ -12722,7 +12690,7 @@
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>Case : wif6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
@@ -12818,10 +12786,8 @@
           <t>Sabin Shrestha</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9818815777</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9818815777</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -12856,10 +12822,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.72209</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.72209</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -12893,10 +12857,8 @@
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH67" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH67" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI67" s="3" t="inlineStr">
         <is>
@@ -12915,20 +12877,16 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.27905</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.27905</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
@@ -13053,10 +13011,8 @@
           <t>Maya K.C</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9841069288</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9841069288</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -13091,10 +13047,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y68" s="3" t="inlineStr">
-        <is>
-          <t>27.73591</t>
-        </is>
+      <c r="Y68" s="3" t="n">
+        <v>27.73591</v>
       </c>
       <c r="Z68" s="3" t="inlineStr">
         <is>
@@ -13150,48 +13104,880 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>85.28792</t>
-        </is>
+      <c r="AP68" s="3" t="n">
+        <v>85.28792</v>
       </c>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 23m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS68" s="3" t="inlineStr">
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:08 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:07:40 PM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:08:29 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr"/>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr"/>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT68" s="3" t="inlineStr">
-        <is>
-          <t>6h 23m</t>
-        </is>
-      </c>
-      <c r="AU68" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV68" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW68" s="3" t="inlineStr">
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>7d 3h 35m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:07 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:07:40 PM</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:08:29 PM</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE70" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF70" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr"/>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr"/>
+      <c r="AM70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>7d 3h 35m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:17 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348488</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:17:21 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.68811</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Near to Green Wood Villas,M7PH+QQ4, Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr">
+        <is>
+          <t>dhakalsrijan59@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>17:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.280293</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:16 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348488</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:17:21 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>27.68811</t>
+        </is>
+      </c>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>Near to Green Wood Villas,M7PH+QQ4, Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr">
+        <is>
+          <t>dhakalsrijan59@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>17:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>85.280293</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -13208,7 +13994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -13245,7 +14031,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -13255,7 +14041,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -13266,7 +14052,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -13278,7 +14064,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>16h 9m</t>
+          <t>17h 39m</t>
         </is>
       </c>
     </row>
@@ -13290,7 +14076,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 34m</t>
+          <t>1d 18h 55m</t>
         </is>
       </c>
     </row>
@@ -13331,14 +14117,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -13399,90 +14185,85 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Sales / Billing Related Issue</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>General Query &amp; Feedback</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -13494,18 +14275,18 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -13517,30 +14298,30 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.8%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -13563,41 +14344,41 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -13609,18 +14390,18 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -13632,14 +14413,14 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -13650,35 +14431,35 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -13696,259 +14477,171 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Sales / Billing Related Issue</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Payment Inquiry</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
-      <c r="B30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
       <c r="C30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>TKT1350187</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Manisha Thapa</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>28 Sep 2026 02:59:56 PM</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:27:10 AM</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>TKT1342919</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Mission shrestha</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Related Issues</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>SKYCOM-No internet connection on STB</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>6d 14h 15m</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>6d 15h 25m</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1342919</t>
+          <t>TKT1350187</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Mission shrestha</t>
+          <t>Manisha Thapa</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -13958,17 +14651,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -13978,64 +14671,64 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 08:03:48 PM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>22 Sep 2026 06:54:03 PM</t>
+          <t>28 Sep 2026 02:59:56 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:19:09 AM</t>
+          <t>29 Sep 2026 10:27:10 AM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>6d 14h 15m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>6d 15h 25m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1350306</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Dipak Rai</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -14045,54 +14738,54 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:56:44 PM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:37:35 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>18h 40m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1349298</t>
+          <t>TKT1342919</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>RAJENDRA BAJRACHARYA</t>
+          <t>Mission shrestha</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -14112,54 +14805,54 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>22 Sep 2026 08:03:48 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:25:28 AM</t>
+          <t>22 Sep 2026 06:54:03 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:32:50 AM</t>
+          <t>29 Sep 2026 10:19:09 AM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>6d 14h 15m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 3h 7m</t>
+          <t>6d 15h 25m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1349403</t>
+          <t>TKT1350306</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Chausara Rai</t>
+          <t>Dipak Rai</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14179,22 +14872,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:23 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:53:58 AM</t>
+          <t>28 Sep 2026 03:56:44 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:00:32 AM</t>
+          <t>29 Sep 2026 10:37:35 AM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -14204,19 +14897,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 6m</t>
+          <t>18h 40m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1348307</t>
+          <t>TKT1349298</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Dada gaun view resort</t>
+          <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -14246,44 +14939,44 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:36:54 PM</t>
+          <t>28 Sep 2026 07:25:28 AM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:33:43 AM</t>
+          <t>29 Sep 2026 10:32:50 AM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 56m</t>
+          <t>1d 3h 7m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1350224</t>
+          <t>TKT1349403</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Anil Balami</t>
+          <t>Chausara Rai</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -14298,12 +14991,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -14313,44 +15006,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>29 Sep 2026 11:00:23 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:16:57 PM</t>
+          <t>28 Sep 2026 08:53:58 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:43:55 AM</t>
+          <t>29 Sep 2026 11:00:32 AM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>20h 26m</t>
+          <t>1d 2h 6m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1350274</t>
+          <t>TKT1348307</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Jitendra kumar Jha</t>
+          <t>Dada gaun view resort</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -14365,12 +15058,12 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -14380,44 +15073,44 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 03:40:48 PM</t>
+          <t>27 Sep 2026 12:36:54 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:25:30 AM</t>
+          <t>29 Sep 2026 11:33:43 AM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>19h 44m</t>
+          <t>1d 22h 56m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1350629</t>
+          <t>TKT1350224</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sambhu Shrestha</t>
+          <t>Anil Balami</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14432,12 +15125,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -14447,54 +15140,54 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 07:17:56 PM</t>
+          <t>28 Sep 2026 03:16:57 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:20 AM</t>
+          <t>29 Sep 2026 11:43:55 AM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>20h 26m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>16h 32m</t>
+          <t>20h 26m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350274</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Jitendra kumar Jha</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -14514,22 +15207,22 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 03:40:48 PM</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:25:30 AM</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
@@ -14539,29 +15232,29 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>19h 44m</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TKT1347929</t>
+          <t>TKT1350629</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Hom ghale</t>
+          <t>Sambhu Shrestha</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14581,22 +15274,22 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:01:25 AM</t>
+          <t>28 Sep 2026 07:17:56 PM</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:54:00 AM</t>
+          <t>29 Sep 2026 11:50:20 AM</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
@@ -14606,29 +15299,29 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>2d 2h 52m</t>
+          <t>16h 32m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TKT1349734</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Shikhar Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -14648,64 +15341,64 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:49:02 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 11:36:00 AM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:50:46 AM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1d 14m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1347929</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Hom ghale</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -14715,44 +15408,44 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>27 Sep 2026 09:01:25 AM</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:54:00 AM</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>2d 2h 52m</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>TKT1350135</t>
+          <t>TKT1349734</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Hemant Shrestha</t>
+          <t>Shikhar Shrestha</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -14767,12 +15460,12 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -14782,44 +15475,44 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>29 Sep 2026 11:49:02 AM</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 02:36:28 PM</t>
+          <t>28 Sep 2026 11:36:00 AM</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:05:05 PM</t>
+          <t>29 Sep 2026 11:50:46 AM</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1m</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>21h 28m</t>
+          <t>1d 14m</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TKT1351251</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Prabuddha Tuladhar</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -14834,12 +15527,12 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -14849,44 +15542,44 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 11:46:16 AM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:29:27 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>TKT1348585</t>
+          <t>TKT1350135</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Achalshail Khadka</t>
+          <t>Hemant Shrestha</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -14901,12 +15594,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -14916,54 +15609,54 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 03:36:18 PM</t>
+          <t>28 Sep 2026 02:36:28 PM</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:23:23 PM</t>
+          <t>29 Sep 2026 12:05:05 PM</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 28m</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 47m</t>
+          <t>21h 28m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TKT1349429</t>
+          <t>TKT1351251</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Sunil Bishwokarma</t>
+          <t>Prabuddha Tuladhar</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14983,22 +15676,22 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 09:14:16 AM</t>
+          <t>29 Sep 2026 11:46:16 AM</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:36:23 PM</t>
+          <t>29 Sep 2026 12:29:27 PM</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -15008,19 +15701,19 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>1d 3h 22m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>TKT1340727</t>
+          <t>TKT1348585</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Kamala gharti magar</t>
+          <t>Achalshail Khadka</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -15035,12 +15728,12 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -15050,54 +15743,54 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 10:43:52 AM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026 08:53:45 PM</t>
+          <t>27 Sep 2026 03:36:18 PM</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:34:36 PM</t>
+          <t>29 Sep 2026 12:23:23 PM</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>1h 50m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>8d 15h 40m</t>
+          <t>1d 20h 47m</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TKT1350683</t>
+          <t>TKT1349429</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Tek Bahadur Budha Magar</t>
+          <t>Sunil Bishwokarma</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -15117,22 +15810,22 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:42 PM</t>
+          <t>28 Sep 2026 09:14:16 AM</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:11:52 PM</t>
+          <t>29 Sep 2026 12:36:23 PM</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -15142,19 +15835,19 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>17h 2m</t>
+          <t>1d 3h 22m</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TKT1348342</t>
+          <t>TKT1340727</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Niroj Bhakta</t>
+          <t>Kamala gharti magar</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -15189,39 +15882,39 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>29 Sep 2026 10:43:52 AM</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:59:48 PM</t>
+          <t>20 Sep 2026 08:53:45 PM</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:20:44 PM</t>
+          <t>29 Sep 2026 12:34:36 PM</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>1h 50m</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>2d 20m</t>
+          <t>8d 15h 40m</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>TKT1349975</t>
+          <t>TKT1350683</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Shanta Chettri</t>
+          <t>Tek Bahadur Budha Magar</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -15251,22 +15944,22 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:36:48 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 01:29:48 PM</t>
+          <t>28 Sep 2026 08:09:42 PM</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:36:48 PM</t>
+          <t>29 Sep 2026 01:11:52 PM</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -15276,19 +15969,19 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>1d 7m</t>
+          <t>17h 2m</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>TKT1348323</t>
+          <t>TKT1348342</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>KOMA. Digital Pvt. Ltd</t>
+          <t>Niroj Bhakta</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -15303,12 +15996,12 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -15318,44 +16011,44 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:53:23 PM</t>
+          <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 12:47:06 PM</t>
+          <t>27 Sep 2026 12:59:48 PM</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:53:23 PM</t>
+          <t>29 Sep 2026 01:20:44 PM</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2d 20m</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>2d 1h 6m</t>
+          <t>2d 20m</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>TKT1348443</t>
+          <t>TKT1349975</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Ajay Pandit</t>
+          <t>Shanta Chettri</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -15365,7 +16058,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -15385,22 +16078,22 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:50:41 PM</t>
+          <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 02:10:40 PM</t>
+          <t>28 Sep 2026 01:29:48 PM</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:50:41 PM</t>
+          <t>29 Sep 2026 01:36:48 PM</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -15410,19 +16103,19 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 40m</t>
+          <t>1d 7m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>TKT1351041</t>
+          <t>TKT1348323</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Niraj kami</t>
+          <t>KOMA. Digital Pvt. Ltd</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -15452,22 +16145,22 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:51:30 PM</t>
+          <t>29 Sep 2026 01:53:23 PM</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 09:49:29 AM</t>
+          <t>27 Sep 2026 12:47:06 PM</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:51:30 PM</t>
+          <t>29 Sep 2026 01:53:23 PM</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
@@ -15477,19 +16170,19 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>4h 2m</t>
+          <t>2d 1h 6m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TKT1348509</t>
+          <t>TKT1348443</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Chiya Mantralaya</t>
+          <t>Ajay Pandit</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -15499,7 +16192,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15519,22 +16212,22 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:30:53 PM</t>
+          <t>29 Sep 2026 01:50:41 PM</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 02:49:19 PM</t>
+          <t>27 Sep 2026 02:10:40 PM</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:30:53 PM</t>
+          <t>29 Sep 2026 01:50:41 PM</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -15544,19 +16237,19 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 41m</t>
+          <t>1d 23h 40m</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>TKT1341368</t>
+          <t>TKT1351041</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Ram Bahadur Kuwar</t>
+          <t>Niraj kami</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -15586,22 +16279,22 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:27:50 PM</t>
+          <t>29 Sep 2026 01:51:30 PM</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>21 Sep 2026 01:55:53 PM</t>
+          <t>29 Sep 2026 09:49:29 AM</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:27:50 PM</t>
+          <t>29 Sep 2026 01:51:30 PM</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -15611,19 +16304,19 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>8d 31m</t>
+          <t>4h 2m</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TKT1349332</t>
+          <t>TKT1348509</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Bishnu Kumar Khadka</t>
+          <t>Chiya Mantralaya</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -15638,12 +16331,12 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -15653,44 +16346,44 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:09:17 AM</t>
+          <t>29 Sep 2026 02:30:53 PM</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:08:08 AM</t>
+          <t>27 Sep 2026 02:49:19 PM</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:34:36 PM</t>
+          <t>29 Sep 2026 02:30:53 PM</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 26m</t>
+          <t>1d 23h 41m</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TKT1347959</t>
+          <t>TKT1341368</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Susila Shah</t>
+          <t>Ram Bahadur Kuwar</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -15720,22 +16413,22 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:49:53 PM</t>
+          <t>29 Sep 2026 02:27:50 PM</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>27 Sep 2026 09:22:32 AM</t>
+          <t>21 Sep 2026 01:55:53 PM</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:49:53 PM</t>
+          <t>29 Sep 2026 02:27:50 PM</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -15745,39 +16438,39 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>2d 5h 27m</t>
+          <t>8d 31m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TKT1349795</t>
+          <t>TKT1349332</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Maniraj Singh Maharjan</t>
+          <t>Bishnu Kumar Khadka</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -15787,44 +16480,44 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:51:12 PM</t>
+          <t>28 Sep 2026 08:09:17 AM</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 12:05:36 PM</t>
+          <t>28 Sep 2026 08:08:08 AM</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:51:12 PM</t>
+          <t>29 Sep 2026 02:34:36 PM</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 6h 25m</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>1d 2h 45m</t>
+          <t>1d 6h 26m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>TKT1350680</t>
+          <t>TKT1347959</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Nikesh tamang</t>
+          <t>Susila Shah</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -15854,22 +16547,22 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:38:55 PM</t>
+          <t>29 Sep 2026 02:49:53 PM</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 08:06:51 PM</t>
+          <t>27 Sep 2026 09:22:32 AM</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:38:55 PM</t>
+          <t>29 Sep 2026 02:49:53 PM</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -15879,39 +16572,39 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>19h 32m</t>
+          <t>2d 5h 27m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>TKT1351404</t>
+          <t>TKT1349795</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Cyrus Shrestha</t>
+          <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -15921,44 +16614,44 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:18:14 PM</t>
+          <t>29 Sep 2026 02:51:12 PM</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:18:14 PM</t>
+          <t>28 Sep 2026 12:05:36 PM</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 03:51:52 PM</t>
+          <t>29 Sep 2026 02:51:12 PM</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2h 33m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>2h 33m</t>
+          <t>1d 2h 45m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>TKT1349548</t>
+          <t>TKT1350680</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Hari Saran Karki</t>
+          <t>Nikesh tamang</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -15988,22 +16681,22 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:11:14 PM</t>
+          <t>29 Sep 2026 03:38:55 PM</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 10:07:13 AM</t>
+          <t>28 Sep 2026 08:06:51 PM</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:11:14 PM</t>
+          <t>29 Sep 2026 03:38:55 PM</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -16013,39 +16706,39 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 4m</t>
+          <t>19h 32m</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TKT1348787</t>
+          <t>TKT1351404</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Hari Budha</t>
+          <t>Cyrus Shrestha</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -16055,44 +16748,44 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:17:54 PM</t>
+          <t>29 Sep 2026 01:18:14 PM</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>27 Sep 2026 05:50:06 PM</t>
+          <t>29 Sep 2026 01:18:14 PM</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:17:54 PM</t>
+          <t>29 Sep 2026 03:51:52 PM</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2h 33m</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>1d 22h 27m</t>
+          <t>2h 33m</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>TKT1350460</t>
+          <t>TKT1349548</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>santoshi shakya</t>
+          <t>Hari Saran Karki</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -16102,17 +16795,17 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -16122,64 +16815,64 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 05:16:24 PM</t>
+          <t>29 Sep 2026 04:11:14 PM</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>28 Sep 2026 04:59:00 PM</t>
+          <t>28 Sep 2026 10:07:13 AM</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:27:32 PM</t>
+          <t>29 Sep 2026 04:11:14 PM</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>23h 28m</t>
+          <t>1d 6h 4m</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TKT1350460</t>
+          <t>TKT1348787</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>santoshi shakya</t>
+          <t>Hari Budha</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Slow Internet Connection</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -16189,44 +16882,44 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 05:16:24 PM</t>
+          <t>29 Sep 2026 04:17:54 PM</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 04:59:00 PM</t>
+          <t>27 Sep 2026 05:50:06 PM</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:27:32 PM</t>
+          <t>29 Sep 2026 04:17:54 PM</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>23h 28m</t>
+          <t>1d 22h 27m</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>TKT1346312</t>
+          <t>TKT1350460</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Basanta Kunwar</t>
+          <t>santoshi shakya</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -16236,7 +16929,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -16256,54 +16949,54 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>25 Sep 2026 04:11:18 PM</t>
+          <t>28 Sep 2026 05:16:24 PM</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>25 Sep 2026 04:11:18 PM</t>
+          <t>28 Sep 2026 04:59:00 PM</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:25:31 PM</t>
+          <t>29 Sep 2026 04:27:32 PM</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>4d 14m</t>
+          <t>23h 11m</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>4d 14m</t>
+          <t>23h 28m</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>TKT1349489</t>
+          <t>TKT1350460</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Mithilesh Thakur</t>
+          <t>santoshi shakya</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -16318,49 +17011,49 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 10:01:37 AM</t>
+          <t>28 Sep 2026 05:16:24 PM</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>28 Sep 2026 09:40:11 AM</t>
+          <t>28 Sep 2026 04:59:00 PM</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:52:31 PM</t>
+          <t>29 Sep 2026 04:27:32 PM</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>1d 6h 50m</t>
+          <t>23h 11m</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>1d 7h 12m</t>
+          <t>23h 28m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>TKT1350899</t>
+          <t>TKT1346312</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Sulaina Shahi</t>
+          <t>Basanta Kunwar</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -16375,136 +17068,136 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:50:53 PM</t>
+          <t>25 Sep 2026 04:11:18 PM</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 07:40:54 AM</t>
+          <t>25 Sep 2026 04:11:18 PM</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:50:53 PM</t>
+          <t>29 Sep 2026 04:25:31 PM</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>4d 14m</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>9h 9m</t>
+          <t>4d 14m</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>TKT1351481</t>
+          <t>TKT1349489</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Punam Kumari Shrestha</t>
+          <t>Mithilesh Thakur</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 05:01:53 PM</t>
+          <t>28 Sep 2026 10:01:37 AM</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 02:07:03 PM</t>
+          <t>28 Sep 2026 09:40:11 AM</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 05:01:53 PM</t>
+          <t>29 Sep 2026 04:52:31 PM</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1d 6h 50m</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>2h 54m</t>
+          <t>1d 7h 12m</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>TKT1351387</t>
+          <t>TKT1350899</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Ritika Thapa</t>
+          <t>Sulaina Shahi</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -16519,27 +17212,27 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:37:53 PM</t>
+          <t>29 Sep 2026 04:50:53 PM</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 01:09:37 PM</t>
+          <t>29 Sep 2026 07:40:54 AM</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:37:53 PM</t>
+          <t>29 Sep 2026 04:50:53 PM</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -16549,19 +17242,19 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>3h 28m</t>
+          <t>9h 9m</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>TKT1351319</t>
+          <t>TKT1351481</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Kalyan Adhikari</t>
+          <t>Punam Kumari Shrestha</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -16586,27 +17279,27 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Case : wif6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>Case : wif6  has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:24:59 PM</t>
+          <t>29 Sep 2026 05:01:53 PM</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 12:17:31 PM</t>
+          <t>29 Sep 2026 02:07:03 PM</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>29 Sep 2026 04:24:59 PM</t>
+          <t>29 Sep 2026 05:01:53 PM</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -16616,42 +17309,176 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>4h 7m</t>
+          <t>2h 54m</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
+          <t>TKT1351387</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Thapa</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:09:37 PM</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>3h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>TKT1351319</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Kalyan Adhikari</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:17:31 PM</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
           <t>TKT1347646</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Sabin Shrestha</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri
 (29 Sep 2026 05:00:45 PM) :
@@ -16666,101 +17493,235 @@
 Related Documents</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 05:00:44 PM</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>26 Sep 2026 07:33:35 PM</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>29 Sep 2026 05:00:44 PM</t>
         </is>
       </c>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
+      <c r="M78" s="3" t="inlineStr">
         <is>
           <t>2d 21h 27m</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>TKT1351071</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Maya K.C</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 04:31:53 PM</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 10:08:24 AM</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>29 Sep 2026 04:31:53 PM</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>6h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348488</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:17:21 PM</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>TKT1348488</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:17:21 PM</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW72"/>
+  <dimension ref="A1:AW73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13214,10 +13214,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -13252,10 +13250,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y69" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z69" s="3" t="inlineStr">
         <is>
@@ -13307,25 +13303,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP69" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -13421,10 +13413,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
@@ -13459,10 +13449,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y70" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z70" s="3" t="inlineStr">
         <is>
@@ -13514,25 +13502,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN70" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
@@ -13628,10 +13612,8 @@
           <t>Srijan Dhakal</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9818999207</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9818999207</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -13666,10 +13648,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" s="3" t="inlineStr">
-        <is>
-          <t>27.68811</t>
-        </is>
+      <c r="Y71" s="3" t="n">
+        <v>27.68811</v>
       </c>
       <c r="Z71" s="3" t="inlineStr">
         <is>
@@ -13725,25 +13705,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.280293</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.280293</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
@@ -13839,10 +13815,8 @@
           <t>Srijan Dhakal</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9818999207</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9818999207</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -13877,10 +13851,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y72" s="3" t="inlineStr">
-        <is>
-          <t>27.68811</t>
-        </is>
+      <c r="Y72" s="3" t="n">
+        <v>27.68811</v>
       </c>
       <c r="Z72" s="3" t="inlineStr">
         <is>
@@ -13936,48 +13908,243 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>85.280293</t>
-        </is>
+      <c r="AP72" s="3" t="n">
+        <v>85.280293</v>
       </c>
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS72" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 37m</t>
-        </is>
-      </c>
-      <c r="AT72" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 37m</t>
-        </is>
-      </c>
-      <c r="AU72" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV72" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:19 PM</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348423</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:19:37 PM</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:01:08 PM</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:19:37 PM</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y73" s="3" t="inlineStr"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA73" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB73" s="3" t="inlineStr">
+        <is>
+          <t>Suraj Mainali</t>
+        </is>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr">
+        <is>
+          <t>Shree Manohar Secondary School - Community school P8P9+XPM Tokha 44600, , ,</t>
+        </is>
+      </c>
+      <c r="AF73" s="3" t="inlineStr">
+        <is>
+          <t>kunwarprem849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG73" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH73" s="3" t="inlineStr"/>
+      <c r="AI73" s="3" t="inlineStr"/>
+      <c r="AJ73" s="3" t="inlineStr"/>
+      <c r="AK73" s="3" t="inlineStr"/>
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO73" s="3" t="inlineStr">
+        <is>
+          <t>L55-5</t>
+        </is>
+      </c>
+      <c r="AP73" s="3" t="inlineStr"/>
+      <c r="AQ73" s="3" t="inlineStr"/>
+      <c r="AR73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -14031,7 +14198,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -14052,7 +14219,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
@@ -14117,14 +14284,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>34</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -14302,14 +14469,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>31</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>81.6%</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17791,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
@@ -17691,7 +17858,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW73"/>
+  <dimension ref="A1:AW75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14018,10 +14018,8 @@
           <t>Prem Bahadur Kunwar</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>9841458042</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>9841458042</v>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
@@ -14107,10 +14105,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN73" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
@@ -14121,30 +14117,440 @@
       <c r="AQ73" s="3" t="inlineStr"/>
       <c r="AR73" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS73" s="3" t="inlineStr">
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:37 PM</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>9708030031</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:37:35 PM</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708030031</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:37:35 PM</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr"/>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA74" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr">
+        <is>
+          <t>Bhotebahal Futsal - Futsal court M8W6+G76 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF74" s="3" t="inlineStr">
+        <is>
+          <t>9708030031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH74" s="3" t="inlineStr"/>
+      <c r="AI74" s="3" t="inlineStr">
+        <is>
+          <t>04:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ74" s="3" t="inlineStr"/>
+      <c r="AK74" s="3" t="inlineStr"/>
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>CDB015</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr"/>
+      <c r="AQ74" s="3" t="inlineStr"/>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT73" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 18m</t>
-        </is>
-      </c>
-      <c r="AU73" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV73" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW73" s="3" t="inlineStr">
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 20m</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW74" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:45 PM</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350858</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Bhatta</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Bhatta</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>9851281562</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:23:39 AM</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>9851281562</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:23:39 AM</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:45:52 PM</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>27.671466</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA75" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB75" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC75" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr">
+        <is>
+          <t>near Subhakamana Party Palace Kirtipur, M7FJ+QWF, Panga Ma Vi Rd, Kirtipur 44600, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF75" s="3" t="inlineStr"/>
+      <c r="AG75" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH75" s="3" t="inlineStr"/>
+      <c r="AI75" s="3" t="inlineStr">
+        <is>
+          <t>07:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ75" s="3" t="inlineStr"/>
+      <c r="AK75" s="3" t="inlineStr"/>
+      <c r="AL75" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO75" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>85.282949</t>
+        </is>
+      </c>
+      <c r="AQ75" s="3" t="inlineStr"/>
+      <c r="AR75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS75" s="3" t="inlineStr">
+        <is>
+          <t>11h 22m</t>
+        </is>
+      </c>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>11h 22m</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW75" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -14161,7 +14567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -14198,7 +14604,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -14208,7 +14614,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -14219,7 +14625,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14637,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 39m</t>
+          <t>17h 9m</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14649,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 18h 55m</t>
+          <t>1d 21h 30m</t>
         </is>
       </c>
     </row>
@@ -14284,14 +14690,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>83.7%</t>
         </is>
       </c>
     </row>
@@ -14469,14 +14875,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -17892,6 +18298,140 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:37:35 PM</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:37:35 PM</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 20m</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>TKT1350858</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Raj Kumar Bhatta</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:23:39 AM</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:23:39 AM</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:45:52 PM</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>11h 22m</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>11h 22m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -14213,10 +14213,8 @@
           <t>Sirjana Gurung</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>9708030031</t>
-        </is>
+      <c r="O74" s="3" t="n">
+        <v>9708030031</v>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
@@ -14306,10 +14304,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN74" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
@@ -14320,7 +14316,7 @@
       <c r="AQ74" s="3" t="inlineStr"/>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
@@ -14416,10 +14412,8 @@
           <t>Raj Kumar Bhatta</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>9851281562</t>
-        </is>
+      <c r="O75" s="3" t="n">
+        <v>9851281562</v>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
@@ -14454,10 +14448,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y75" s="3" t="inlineStr">
-        <is>
-          <t>27.671466</t>
-        </is>
+      <c r="Y75" s="3" t="n">
+        <v>27.671466</v>
       </c>
       <c r="Z75" s="3" t="inlineStr">
         <is>
@@ -14509,25 +14501,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN75" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN75" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>85.282949</t>
-        </is>
+      <c r="AP75" s="3" t="n">
+        <v>85.282949</v>
       </c>
       <c r="AQ75" s="3" t="inlineStr"/>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
@@ -18331,7 +18319,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -18398,7 +18386,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW75"/>
+  <dimension ref="A1:AW76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14544,6 +14544,217 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 7:07 PM</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351709</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Rakesh shrestha</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>Rakesh shrestha</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>9813632008</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:07:28 PM</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="3" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>9813632008</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:53:59 PM</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:07:28 PM</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>27.717205</t>
+        </is>
+      </c>
+      <c r="Z76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA76" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB76" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr">
+        <is>
+          <t>Samata Shiksha Niketan School , P986+R99, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF76" s="3" t="inlineStr">
+        <is>
+          <t>shrestharakesh23@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH76" s="3" t="inlineStr"/>
+      <c r="AI76" s="3" t="inlineStr">
+        <is>
+          <t>02:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ76" s="3" t="inlineStr"/>
+      <c r="AK76" s="3" t="inlineStr"/>
+      <c r="AL76" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO76" s="3" t="inlineStr">
+        <is>
+          <t>L28-3</t>
+        </is>
+      </c>
+      <c r="AP76" s="3" t="inlineStr">
+        <is>
+          <t>85.360938</t>
+        </is>
+      </c>
+      <c r="AQ76" s="3" t="inlineStr"/>
+      <c r="AR76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>2h 13m</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW76" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14555,7 +14766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -14592,7 +14803,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -14602,7 +14813,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -14613,7 +14824,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -14625,7 +14836,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>17h 9m</t>
+          <t>16h 48m</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14848,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 30m</t>
+          <t>1d 20h 37m</t>
         </is>
       </c>
     </row>
@@ -14678,14 +14889,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.1%</t>
         </is>
       </c>
     </row>
@@ -14863,14 +15074,14 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -18420,6 +18631,73 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351709</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Rakesh shrestha</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:07:28 PM</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:53:59 PM</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:07:28 PM</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>2h 13m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_29_Sep_2026.xlsx
+++ b/audit_report_ALL_TEAM_29_Sep_2026.xlsx
@@ -14611,10 +14611,8 @@
           <t>Rakesh shrestha</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>9813632008</t>
-        </is>
+      <c r="O76" s="3" t="n">
+        <v>9813632008</v>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
@@ -14649,10 +14647,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y76" s="3" t="inlineStr">
-        <is>
-          <t>27.717205</t>
-        </is>
+      <c r="Y76" s="3" t="n">
+        <v>27.717205</v>
       </c>
       <c r="Z76" s="3" t="inlineStr">
         <is>
@@ -14708,25 +14704,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN76" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN76" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
           <t>L28-3</t>
         </is>
       </c>
-      <c r="AP76" s="3" t="inlineStr">
-        <is>
-          <t>85.360938</t>
-        </is>
+      <c r="AP76" s="3" t="n">
+        <v>85.360938</v>
       </c>
       <c r="AQ76" s="3" t="inlineStr"/>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
@@ -18664,7 +18656,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
